--- a/data/gravel/Stanton Sherpa GenV 2025.xlsx
+++ b/data/gravel/Stanton Sherpa GenV 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E77BEBCE-4A11-0A42-9C8D-D0612CB203C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA176B81-1A01-784B-B2A9-4B62FC39843A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5640" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="119">
   <si>
     <t>brand</t>
   </si>
@@ -341,12 +341,6 @@
     <t>https://www.stantonbikes.com/collections/sherpa-genv</t>
   </si>
   <si>
-    <t>this is 120 fork at 25% sag, see Sherpa Ti</t>
-  </si>
-  <si>
-    <t>not specified. Fox 120 fork. My estimate is 40</t>
-  </si>
-  <si>
     <t>https://www.stantonbikes.com/cdn/shop/files/SHERPA_GEN_V_HERO_SHOT_2_extended_750x.jpg?v=1749118241</t>
   </si>
   <si>
@@ -384,6 +378,18 @@
   </si>
   <si>
     <t>100-130</t>
+  </si>
+  <si>
+    <t>20% + 15</t>
+  </si>
+  <si>
+    <t>travel</t>
+  </si>
+  <si>
+    <t>30% + 15</t>
+  </si>
+  <si>
+    <t>I think this means that the fork ac + 15 is the length from axle to head tube</t>
   </si>
 </sst>
 </file>
@@ -426,11 +432,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -727,7 +735,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -775,7 +783,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -783,7 +791,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -966,7 +974,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -986,7 +994,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -1006,7 +1014,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -1026,7 +1034,7 @@
         <v>75.5</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -1046,10 +1054,10 @@
         <v>500</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>18</v>
       </c>
@@ -1068,13 +1076,33 @@
       <c r="F21">
         <v>47</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H21" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="I21">
+        <v>100</v>
+      </c>
+      <c r="J21">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H22" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="I22">
+        <f>505 -$H22*I$21</f>
+        <v>485</v>
+      </c>
+      <c r="J22">
+        <f>530 -$H22*J$21</f>
+        <v>506</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -1090,50 +1118,81 @@
       <c r="F23">
         <v>44</v>
       </c>
-      <c r="G23" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G23" s="1"/>
+      <c r="H23" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I23">
+        <f>I22+15</f>
+        <v>500</v>
+      </c>
+      <c r="J23">
+        <f>J22+15</f>
+        <v>521</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C24">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D24">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E24">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F24">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G24" s="1"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H24" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="I24">
+        <f>505 -$H24*I$21</f>
+        <v>475</v>
+      </c>
+      <c r="J24">
+        <f>530 -$H24*J$21</f>
+        <v>494</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G25" s="1"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H25" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I25">
+        <f>I24+15</f>
+        <v>490</v>
+      </c>
+      <c r="J25">
+        <f>J24+15</f>
+        <v>509</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>24</v>
       </c>
@@ -1141,7 +1200,7 @@
         <v>2700</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>25</v>
       </c>
@@ -1158,7 +1217,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>26</v>
       </c>
@@ -1175,7 +1234,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>27</v>
       </c>
@@ -1312,7 +1371,7 @@
         <v>37</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
@@ -1320,16 +1379,13 @@
         <v>38</v>
       </c>
       <c r="B46">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>39</v>
       </c>
-      <c r="B47">
-        <v>120</v>
-      </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
@@ -1354,32 +1410,32 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
@@ -1536,10 +1592,10 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B81" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
